--- a/checklists/excel/techlead/design.xlsx
+++ b/checklists/excel/techlead/design.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Design" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Design Compliance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,94 +425,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item Text</t>
+          <t>Sr.No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Main Category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Sub Category</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>How to Measure</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Architecture aligns with system design (MUST)</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>Design Compliance Review</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Follows established architecture patterns; Integrates properly with existing systems; Maintains separation of concerns</t>
+          <t>Verify project structure is logically separated</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Implementation should align with the overall system architecture</t>
+          <t>Ensure the project is organized into distinct packages like model, view, fragment to maintain clear separation of concern as per design.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Follows SOLID principles</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Run ArchUnit tests</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Scalability and maintainability considered (GOOD)</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>Design Compliance Review</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Performance bottlenecks identified; Future extensibility planned; Code maintainability ensured</t>
+          <t>Check for proper dependency injection</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Design should support future growth and maintenance</t>
+          <t>Verify that dependencies are properly injected and not hard-coded, following dependency inversion principle.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Uses DI framework (Dagger/Hilt) correctly</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Review dependency graph and check for circular dependencies</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Security best practices implemented (MUST)</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>Design Compliance Review</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Input validation implemented; Authentication/authorization proper; Sensitive data protected</t>
+          <t>Validate architectural patterns</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Security considerations should be properly addressed</t>
+          <t>Ensure the code follows established architectural patterns like MVP, MVVM, or Clean Architecture.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Implements chosen architecture consistently</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Code review and static analysis tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Design Compliance Review</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Check for proper error handling</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Verify that error handling is implemented consistently across the application with proper error boundaries.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Uses Result/Either pattern or proper exception handling</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Test error scenarios and review error handling code</t>
         </is>
       </c>
     </row>
